--- a/data/rme_site-info.xlsx
+++ b/data/rme_site-info.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucc-my.sharepoint.com/personal/chris_bird_tamucc_edu/Documents/!students/Labrador_Dissertation/09_github-repositories/kll_chapter2_edna-optimization/data/for_dryad/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucc-my.sharepoint.com/personal/chris_bird_tamucc_edu/Documents/!students/Labrador_Dissertation/09_github-repositories/kll_chapter2_edna-optimization/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8AB1E0A-D6D3-495A-8689-13450A9CD436}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA0D30A8-12AD-4D5B-97C1-166E8DEA0035}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +45,25 @@
     <author>tc={621F18AF-D926-45D5-8E1C-5A21E5AA15C8}</author>
   </authors>
   <commentList>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{621F18AF-D926-45D5-8E1C-5A21E5AA15C8}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{621F18AF-D926-45D5-8E1C-5A21E5AA15C8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    accidentally treated as medium-low during sampling</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={9C5AB5D0-E50B-4B22-AB08-75351E84755C}</author>
+  </authors>
+  <commentList>
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{9C5AB5D0-E50B-4B22-AB08-75351E84755C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -54,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="53">
   <si>
     <t>site</t>
   </si>
@@ -74,6 +96,15 @@
     <t>depth_ft</t>
   </si>
   <si>
+    <t>utm-zone</t>
+  </si>
+  <si>
+    <t>easting</t>
+  </si>
+  <si>
+    <t>northing</t>
+  </si>
+  <si>
     <t>latitude</t>
   </si>
   <si>
@@ -95,6 +126,9 @@
     <t>medium</t>
   </si>
   <si>
+    <t>55P</t>
+  </si>
+  <si>
     <t>Cave Museum</t>
   </si>
   <si>
@@ -155,6 +189,9 @@
     <t>AGT</t>
   </si>
   <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>Okgok</t>
   </si>
   <si>
@@ -188,24 +225,28 @@
     <t>Agatasi</t>
   </si>
   <si>
-    <t xml:space="preserve">medium-high </t>
-  </si>
-  <si>
     <t>Sailigai Point</t>
   </si>
   <si>
     <t>date_and_time_collection</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>depth_m</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm"/>
+    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +259,20 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -240,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -265,6 +320,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -587,7 +651,15 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C11" dT="2024-02-12T16:46:24.71" personId="{9D351B5B-4401-41FC-A17F-8235BBF24252}" id="{621F18AF-D926-45D5-8E1C-5A21E5AA15C8}">
+  <threadedComment ref="C10" dT="2024-02-12T16:46:24.71" personId="{9D351B5B-4401-41FC-A17F-8235BBF24252}" id="{621F18AF-D926-45D5-8E1C-5A21E5AA15C8}">
+    <text>accidentally treated as medium-low during sampling</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C10" dT="2024-02-12T16:46:24.71" personId="{9D351B5B-4401-41FC-A17F-8235BBF24252}" id="{9C5AB5D0-E50B-4B22-AB08-75351E84755C}">
     <text>accidentally treated as medium-low during sampling</text>
   </threadedComment>
 </ThreadedComments>
@@ -595,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="2" width="15.54296875" customWidth="1"/>
@@ -603,11 +675,13 @@
     <col min="4" max="4" width="24.453125" style="8" customWidth="1"/>
     <col min="5" max="5" width="20.6796875" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.54296875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" style="6" customWidth="1"/>
-    <col min="8" max="9" width="15.54296875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="21.90625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="13" width="15.54296875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -618,7 +692,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -629,388 +703,872 @@
       <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
+      <c r="K1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" s="9">
+        <v>45234.53125</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="6">
+        <v>67</v>
+      </c>
+      <c r="H2" s="10">
+        <v>20.420000000000002</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="2">
+        <v>315190</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1569845</v>
+      </c>
+      <c r="L2" s="2">
+        <v>14.193870597143601</v>
+      </c>
+      <c r="M2" s="2">
+        <v>145.287430434306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="9">
+        <v>45234.631944444445</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="6">
+        <v>59.5</v>
+      </c>
+      <c r="H3" s="10">
+        <v>18.14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="2">
+        <v>14.119814</v>
+      </c>
+      <c r="M3" s="2">
+        <v>145.21903399999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="9">
+        <v>45234.677083333336</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="6">
+        <v>25.4</v>
+      </c>
+      <c r="H4" s="10">
+        <v>7.74</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2">
+        <v>302264</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1561542</v>
+      </c>
+      <c r="L4" s="2">
+        <v>14.1179480911628</v>
+      </c>
+      <c r="M4" s="2">
+        <v>145.16829334532301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="9">
+        <v>45234.381249999999</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="6">
+        <v>61</v>
+      </c>
+      <c r="H5" s="10">
+        <v>18.59</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="2">
+        <v>300272</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1565959</v>
+      </c>
+      <c r="L5" s="2">
+        <v>14.1577240548057</v>
+      </c>
+      <c r="M5" s="2">
+        <v>145.14952469340599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="9">
+        <v>45234.445833333331</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="6">
+        <v>33.1</v>
+      </c>
+      <c r="H6" s="10">
+        <v>10.09</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="2">
+        <v>305597</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1568509</v>
+      </c>
+      <c r="L6" s="2">
+        <v>14.181144585198901</v>
+      </c>
+      <c r="M6" s="2">
+        <v>145.198661311915</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="9">
+        <v>45234.722916666666</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="6">
+        <v>45.2</v>
+      </c>
+      <c r="H7" s="10">
+        <v>13.78</v>
+      </c>
+      <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="2">
+        <v>297203</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1561560</v>
+      </c>
+      <c r="L7" s="2">
+        <v>14.117749417885801</v>
+      </c>
+      <c r="M7" s="2">
+        <v>145.12142764631199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="9">
+        <v>45234.711805555555</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="6">
+        <v>29</v>
+      </c>
+      <c r="H8" s="10">
+        <v>8.84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="2">
+        <v>300689</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1563495</v>
+      </c>
+      <c r="L8" s="2">
+        <v>14.135486230838399</v>
+      </c>
+      <c r="M8" s="2">
+        <v>145.15356656486199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="9">
+        <v>45234.505555555559</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="6">
+        <v>29.9</v>
+      </c>
+      <c r="H9" s="10">
+        <v>9.11</v>
+      </c>
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="2">
+        <v>309566</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1570541</v>
+      </c>
+      <c r="L9" s="2">
+        <v>14.1997824187648</v>
+      </c>
+      <c r="M9" s="2">
+        <v>145.23528338662399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="9">
+        <v>45234.640277777777</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="6">
+        <v>36.5</v>
+      </c>
+      <c r="H10" s="10">
+        <v>11.13</v>
+      </c>
+      <c r="I10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="2">
+        <v>305381</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1560908</v>
+      </c>
+      <c r="L10" s="2">
+        <v>14.112436381821899</v>
+      </c>
+      <c r="M10" s="2">
+        <v>145.19720217846699</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9">
+        <v>45234.48333333333</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="6">
+        <v>51</v>
+      </c>
+      <c r="H11" s="10">
+        <v>15.54</v>
+      </c>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="2">
+        <v>307655</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1569512</v>
+      </c>
+      <c r="L11" s="2">
+        <v>14.1903516994978</v>
+      </c>
+      <c r="M11" s="2">
+        <v>145.21765330295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9">
+        <v>45234.545138888891</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="6">
+        <v>25.8</v>
+      </c>
+      <c r="H12" s="10">
+        <v>7.86</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="2">
+        <v>313064</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1565114</v>
+      </c>
+      <c r="L12" s="2">
+        <v>14.1509715047572</v>
+      </c>
+      <c r="M12" s="2">
+        <v>145.26806035837799</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="9">
+        <v>45234.416666666664</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="6">
+        <v>30.4</v>
+      </c>
+      <c r="H13" s="10">
+        <v>9.27</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="2">
+        <v>301051</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1566771</v>
+      </c>
+      <c r="L13" s="2">
+        <v>14.165117760327099</v>
+      </c>
+      <c r="M13" s="2">
+        <v>145.15668023722799</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="9">
         <v>45234.318055555559</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="6">
+        <v>22.6</v>
+      </c>
+      <c r="H14" s="10">
+        <v>6.89</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="2">
+        <v>298230</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1563816</v>
+      </c>
+      <c r="L14" s="2">
+        <v>14.138211092091501</v>
+      </c>
+      <c r="M14" s="2">
+        <v>145.13077105236999</v>
+      </c>
+    </row>
+    <row r="19" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+    </row>
+    <row r="28" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+    </row>
+    <row r="32" spans="7:8" x14ac:dyDescent="0.75">
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M14">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9302D867-1513-4D90-A5B5-4DC04504A4DF}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="29.40625" customWidth="1"/>
+    <col min="4" max="4" width="24.453125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="21.58984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="9">
+        <v>45234.53125</v>
+      </c>
+      <c r="F2" s="12">
+        <v>45234.53125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="9">
+        <v>45234.631944444445</v>
+      </c>
+      <c r="F3" s="12">
+        <v>45234.631944444445</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="9">
+        <v>45234.677083333336</v>
+      </c>
+      <c r="F4" s="12">
+        <v>45234.677083333336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="9">
+        <v>45234.381249999999</v>
+      </c>
+      <c r="F5" s="12">
+        <v>45234.381249999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="9">
+        <v>45234.445833333331</v>
+      </c>
+      <c r="F6" s="12">
+        <v>45234.445833333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="9">
+        <v>45234.722916666666</v>
+      </c>
+      <c r="F7" s="12">
+        <v>45234.722916666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="9">
+        <v>45234.711805555555</v>
+      </c>
+      <c r="F8" s="12">
+        <v>45234.711805555555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="9">
+        <v>45234.505555555559</v>
+      </c>
+      <c r="F9" s="12">
+        <v>45234.505555555559</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="9">
+        <v>45234.640277777777</v>
+      </c>
+      <c r="F10" s="12">
+        <v>45234.640277777777</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9">
+        <v>45234.48333333333</v>
+      </c>
+      <c r="F11" s="12">
+        <v>45234.48333333333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9">
+        <v>45234.545138888891</v>
+      </c>
+      <c r="F12" s="12">
+        <v>45234.545138888891</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="9">
+        <v>45234.416666666664</v>
+      </c>
+      <c r="F13" s="12">
+        <v>45234.416666666664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="6">
-        <v>22.6</v>
-      </c>
-      <c r="H2" s="2">
-        <v>14.138211092091501</v>
-      </c>
-      <c r="I2" s="2">
-        <v>145.13077105236999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
+      <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="9">
-        <v>45234.381249999999</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="6">
-        <v>61</v>
-      </c>
-      <c r="H3" s="2">
-        <v>14.1577240548057</v>
-      </c>
-      <c r="I3" s="2">
-        <v>145.14952469340599</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="9">
-        <v>45234.416666666664</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="6">
-        <v>30.4</v>
-      </c>
-      <c r="H4" s="2">
-        <v>14.165117760327099</v>
-      </c>
-      <c r="I4" s="2">
-        <v>145.15668023722799</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="9">
-        <v>45234.445833333331</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6">
-        <v>33.1</v>
-      </c>
-      <c r="H5" s="2">
-        <v>14.181144585198901</v>
-      </c>
-      <c r="I5" s="2">
-        <v>145.198661311915</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="9">
-        <v>45234.48333333333</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="6">
-        <v>51</v>
-      </c>
-      <c r="H6" s="2">
-        <v>14.1903516994978</v>
-      </c>
-      <c r="I6" s="2">
-        <v>145.21765330295</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="9">
-        <v>45234.505555555559</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="6">
-        <v>29.9</v>
-      </c>
-      <c r="H7" s="2">
-        <v>14.1997824187648</v>
-      </c>
-      <c r="I7" s="2">
-        <v>145.23528338662399</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="9">
-        <v>45234.53125</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="6">
-        <v>67</v>
-      </c>
-      <c r="H8" s="2">
-        <v>14.193870597143601</v>
-      </c>
-      <c r="I8" s="2">
-        <v>145.287430434306</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="9">
-        <v>45234.545138888891</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="6">
-        <v>25.8</v>
-      </c>
-      <c r="H9" s="2">
-        <v>14.1509715047572</v>
-      </c>
-      <c r="I9" s="2">
-        <v>145.26806035837799</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="9">
-        <v>45234.631944444445</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="6">
-        <v>59.5</v>
-      </c>
-      <c r="H10" s="2">
-        <v>14.119814</v>
-      </c>
-      <c r="I10" s="2">
-        <v>145.21903399999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="9">
-        <v>45234.640277777777</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="6">
-        <v>36.5</v>
-      </c>
-      <c r="H11" s="2">
-        <v>14.112436381821899</v>
-      </c>
-      <c r="I11" s="2">
-        <v>145.19720217846699</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="9">
-        <v>45234.677083333336</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="6">
-        <v>25.4</v>
-      </c>
-      <c r="H12" s="2">
-        <v>14.1179480911628</v>
-      </c>
-      <c r="I12" s="2">
-        <v>145.16829334532301</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="9">
-        <v>45234.711805555555</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="6">
-        <v>29</v>
-      </c>
-      <c r="H13" s="2">
-        <v>14.135486230838399</v>
-      </c>
-      <c r="I13" s="2">
-        <v>145.15356656486199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
       <c r="D14" s="9">
-        <v>45234.722916666666</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="6">
-        <v>45.2</v>
-      </c>
-      <c r="H14" s="2">
-        <v>14.117749417885801</v>
-      </c>
-      <c r="I14" s="2">
-        <v>145.12142764631199</v>
+        <v>45234.318055555559</v>
+      </c>
+      <c r="F14" s="12">
+        <v>45234.318055555559</v>
       </c>
     </row>
   </sheetData>
